--- a/data/trans_dic/P16A06-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P16A06-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido pastillas para dormir en las dos últimas semanas</t>
+          <t>Población que ha consumido pastillas para dormir en las dos últimas semanas (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,57; 2,22</t>
+          <t>0,56; 2,34</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,03; 3,12</t>
+          <t>1,04; 2,94</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,4; 3,76</t>
+          <t>1,44; 3,87</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,16; 8,69</t>
+          <t>5,03; 8,78</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,94; 2,83</t>
+          <t>0,91; 2,91</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,47; 6,65</t>
+          <t>3,38; 6,6</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,7; 11,13</t>
+          <t>6,57; 10,98</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10,62; 14,03</t>
+          <t>10,45; 14,15</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,9; 2,16</t>
+          <t>0,94; 2,14</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,47; 4,35</t>
+          <t>2,44; 4,29</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4,39; 6,97</t>
+          <t>4,42; 6,87</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,22; 10,92</t>
+          <t>8,23; 10,91</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,9; 2,63</t>
+          <t>0,96; 2,66</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,53; 1,91</t>
+          <t>0,52; 1,92</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,58; 3,72</t>
+          <t>1,59; 3,74</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,59; 4,25</t>
+          <t>1,45; 4,25</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,28; 4,68</t>
+          <t>2,29; 4,69</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,09; 9,57</t>
+          <t>6,0; 9,63</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,42; 7,29</t>
+          <t>4,28; 7,27</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,04; 10,97</t>
+          <t>8,07; 11,03</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,85; 3,37</t>
+          <t>1,83; 3,31</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,54; 5,37</t>
+          <t>3,54; 5,43</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3,16; 4,96</t>
+          <t>3,29; 5,03</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,92; 7,09</t>
+          <t>3,99; 7,06</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,07; 3,28</t>
+          <t>1,01; 3,21</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,35; 4,11</t>
+          <t>1,35; 3,99</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,48; 3,85</t>
+          <t>1,53; 3,84</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,45; 6,35</t>
+          <t>3,44; 6,45</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,01; 7,47</t>
+          <t>4,0; 7,27</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,8; 7,48</t>
+          <t>3,72; 7,35</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,13; 8,95</t>
+          <t>5,0; 8,92</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,46; 9,85</t>
+          <t>3,48; 9,92</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,79; 4,71</t>
+          <t>2,8; 4,82</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,95; 5,15</t>
+          <t>2,98; 5,26</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,74; 5,97</t>
+          <t>3,72; 6,03</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,75; 7,45</t>
+          <t>3,99; 7,52</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,06; 4,25</t>
+          <t>2,05; 4,2</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,86; 4,31</t>
+          <t>1,92; 4,45</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,05; 4,41</t>
+          <t>2,13; 4,42</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,76; 7,87</t>
+          <t>4,84; 7,88</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,39; 7,38</t>
+          <t>4,46; 7,24</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,16; 8,1</t>
+          <t>5,09; 8,2</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,15; 11,25</t>
+          <t>7,28; 11,13</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,76; 13,22</t>
+          <t>8,61; 12,95</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,54; 5,43</t>
+          <t>3,57; 5,47</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,87; 5,93</t>
+          <t>3,96; 5,94</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5,16; 7,51</t>
+          <t>5,21; 7,45</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>7,57; 10,09</t>
+          <t>7,57; 10,15</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,54; 2,47</t>
+          <t>1,53; 2,53</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,54; 2,63</t>
+          <t>1,59; 2,59</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,17; 3,31</t>
+          <t>2,1; 3,21</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,79; 5,7</t>
+          <t>3,75; 5,61</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,46; 4,86</t>
+          <t>3,5; 4,88</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,44; 7,17</t>
+          <t>5,55; 7,09</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,62; 8,4</t>
+          <t>6,62; 8,5</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>8,32; 10,99</t>
+          <t>7,96; 10,91</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,71; 3,54</t>
+          <t>2,65; 3,51</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3,71; 4,68</t>
+          <t>3,79; 4,76</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4,59; 5,75</t>
+          <t>4,62; 5,72</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,39; 8,13</t>
+          <t>6,46; 8,16</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido pastillas para dormir en las dos últimas semanas</t>
+          <t>Población que ha consumido pastillas para dormir en las dos últimas semanas (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3959; 15390</t>
+          <t>3847; 16187</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7196; 21864</t>
+          <t>7275; 20642</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9473; 25353</t>
+          <t>9715; 26147</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>32790; 55199</t>
+          <t>31935; 55741</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>6486; 19489</t>
+          <t>6252; 20026</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>24032; 46012</t>
+          <t>23399; 45719</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>45080; 74880</t>
+          <t>44186; 73900</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>71720; 94790</t>
+          <t>70608; 95583</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>12423; 29888</t>
+          <t>13030; 29570</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>34372; 60698</t>
+          <t>34052; 59846</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>59186; 93949</t>
+          <t>59624; 92613</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>107657; 143107</t>
+          <t>107901; 142960</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8611; 25330</t>
+          <t>9277; 25603</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5360; 19447</t>
+          <t>5250; 19514</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16113; 38035</t>
+          <t>16251; 38238</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18930; 50695</t>
+          <t>17339; 50696</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>22108; 45368</t>
+          <t>22170; 45388</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>62585; 98323</t>
+          <t>61640; 98945</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>46065; 75978</t>
+          <t>44588; 75856</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>76978; 105075</t>
+          <t>77299; 105667</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>35721; 65039</t>
+          <t>35322; 63809</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>72248; 109749</t>
+          <t>72404; 110925</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>65200; 102358</t>
+          <t>67953; 103963</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>84329; 152530</t>
+          <t>85738; 151782</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>7232; 22252</t>
+          <t>6850; 21811</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>10211; 31111</t>
+          <t>10177; 30162</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11243; 29234</t>
+          <t>11656; 29174</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>24275; 44693</t>
+          <t>24175; 45391</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>27437; 51092</t>
+          <t>27367; 49714</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>29504; 58062</t>
+          <t>28856; 57066</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>40241; 70288</t>
+          <t>39270; 70013</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>32241; 91872</t>
+          <t>32490; 92471</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>38042; 64170</t>
+          <t>38141; 65636</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>45228; 78881</t>
+          <t>45617; 80567</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>57810; 92226</t>
+          <t>57400; 93064</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>61377; 121841</t>
+          <t>65299; 123083</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>19387; 40024</t>
+          <t>19342; 39580</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>17597; 40645</t>
+          <t>18152; 42012</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>19235; 41357</t>
+          <t>19939; 41475</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>44133; 72940</t>
+          <t>44846; 73047</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>45622; 76607</t>
+          <t>46312; 75236</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>54112; 84899</t>
+          <t>53378; 85978</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>74605; 117376</t>
+          <t>75967; 116153</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>95608; 144260</t>
+          <t>94006; 141363</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>70204; 107485</t>
+          <t>70647; 108393</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>77090; 118081</t>
+          <t>78919; 118363</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>102181; 148729</t>
+          <t>103190; 147709</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>152832; 203572</t>
+          <t>152764; 204919</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>50520; 80965</t>
+          <t>50187; 82874</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>52781; 90023</t>
+          <t>54220; 88623</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>73728; 112248</t>
+          <t>71362; 109099</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>131136; 196992</t>
+          <t>129731; 193911</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>116772; 164191</t>
+          <t>118361; 165057</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>192835; 254178</t>
+          <t>196652; 251511</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>234670; 297806</t>
+          <t>234505; 301382</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>304452; 401918</t>
+          <t>291033; 399005</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>180172; 235616</t>
+          <t>176275; 233535</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>258055; 326046</t>
+          <t>263880; 331559</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>318409; 399037</t>
+          <t>320372; 396633</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>455011; 578475</t>
+          <t>459592; 580537</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P16A06-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P16A06-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,36%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,56; 2,34</t>
+          <t>0,56; 2,33</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,04; 2,94</t>
+          <t>1,0; 3,14</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,44; 3,87</t>
+          <t>1,42; 3,98</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,03; 8,78</t>
+          <t>4,81; 8,44</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,91; 2,91</t>
+          <t>0,87; 2,9</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,38; 6,6</t>
+          <t>3,52; 6,8</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,57; 10,98</t>
+          <t>6,45; 10,83</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10,45; 14,15</t>
+          <t>10,13; 13,88</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,94; 2,14</t>
+          <t>0,95; 2,28</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,44; 4,29</t>
+          <t>2,49; 4,37</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4,42; 6,87</t>
+          <t>4,39; 6,98</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,23; 10,91</t>
+          <t>8,18; 10,77</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>6,59%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,96; 2,66</t>
+          <t>0,91; 2,72</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,52; 1,92</t>
+          <t>0,53; 1,89</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,59; 3,74</t>
+          <t>1,61; 3,66</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,45; 4,25</t>
+          <t>2,85; 5,15</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,29; 4,69</t>
+          <t>2,29; 4,75</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,0; 9,63</t>
+          <t>6,19; 9,59</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,28; 7,27</t>
+          <t>4,41; 7,26</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,07; 11,03</t>
+          <t>7,9; 10,85</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,83; 3,31</t>
+          <t>1,82; 3,24</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,54; 5,43</t>
+          <t>3,55; 5,43</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3,29; 5,03</t>
+          <t>3,28; 5,12</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,99; 7,06</t>
+          <t>5,67; 7,62</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,96%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,01; 3,21</t>
+          <t>0,96; 3,22</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,35; 3,99</t>
+          <t>1,34; 4,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,53; 3,84</t>
+          <t>1,42; 3,86</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,44; 6,45</t>
+          <t>3,5; 6,71</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,0; 7,27</t>
+          <t>3,94; 7,32</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,72; 7,35</t>
+          <t>3,85; 7,15</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,0; 8,92</t>
+          <t>5,16; 9,08</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,48; 9,92</t>
+          <t>7,48; 11,01</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,8; 4,82</t>
+          <t>2,8; 4,89</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,98; 5,26</t>
+          <t>2,92; 5,13</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,72; 6,03</t>
+          <t>3,66; 6,03</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,99; 7,52</t>
+          <t>5,87; 8,21</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,74%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,05; 4,2</t>
+          <t>2,06; 4,11</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,92; 4,45</t>
+          <t>1,98; 4,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,13; 4,42</t>
+          <t>2,18; 4,46</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,84; 7,88</t>
+          <t>4,55; 7,56</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,46; 7,24</t>
+          <t>4,33; 7,32</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,09; 8,2</t>
+          <t>5,08; 8,12</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,28; 11,13</t>
+          <t>7,12; 11,07</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,61; 12,95</t>
+          <t>9,87; 12,88</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,57; 5,47</t>
+          <t>3,61; 5,44</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,96; 5,94</t>
+          <t>3,93; 5,97</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5,21; 7,45</t>
+          <t>5,1; 7,49</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>7,57; 10,15</t>
+          <t>7,79; 9,78</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,84%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,53; 2,53</t>
+          <t>1,57; 2,55</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,59; 2,59</t>
+          <t>1,52; 2,61</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,1; 3,21</t>
+          <t>2,14; 3,33</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,75; 5,61</t>
+          <t>4,49; 5,96</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,5; 4,88</t>
+          <t>3,51; 4,9</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,55; 7,09</t>
+          <t>5,54; 7,11</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,62; 8,5</t>
+          <t>6,7; 8,52</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>7,96; 10,91</t>
+          <t>9,58; 11,22</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,65; 3,51</t>
+          <t>2,71; 3,52</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3,79; 4,76</t>
+          <t>3,75; 4,76</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4,62; 5,72</t>
+          <t>4,62; 5,7</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,46; 8,16</t>
+          <t>7,29; 8,41</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>42129</t>
+          <t>44846</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>82541</t>
+          <t>88298</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>124670</t>
+          <t>133144</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3847; 16187</t>
+          <t>3900; 16120</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7275; 20642</t>
+          <t>6995; 21997</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9715; 26147</t>
+          <t>9557; 26851</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>31935; 55741</t>
+          <t>33208; 58228</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>6252; 20026</t>
+          <t>5976; 19959</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>23399; 45719</t>
+          <t>24358; 47095</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>44186; 73900</t>
+          <t>43403; 72881</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>70608; 95583</t>
+          <t>74197; 101676</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>13030; 29570</t>
+          <t>13171; 31452</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>34052; 59846</t>
+          <t>34747; 60922</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>59624; 92613</t>
+          <t>59220; 94051</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>107901; 142960</t>
+          <t>116464; 153278</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>35301</t>
+          <t>40091</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>91105</t>
+          <t>99460</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>126405</t>
+          <t>139551</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9277; 25603</t>
+          <t>8713; 26173</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5250; 19514</t>
+          <t>5358; 19190</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16251; 38238</t>
+          <t>16431; 37389</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17339; 50696</t>
+          <t>29853; 54014</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>22170; 45388</t>
+          <t>22170; 46038</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>61640; 98945</t>
+          <t>63597; 98561</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>44588; 75856</t>
+          <t>45962; 75669</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>77299; 105667</t>
+          <t>84588; 116121</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>35322; 63809</t>
+          <t>35063; 62548</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>72404; 110925</t>
+          <t>72596; 110898</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>67953; 103963</t>
+          <t>67840; 105677</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>85738; 151782</t>
+          <t>120152; 161420</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>33294</t>
+          <t>39507</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>66224</t>
+          <t>72697</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>99518</t>
+          <t>112205</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>6850; 21811</t>
+          <t>6546; 21865</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>10177; 30162</t>
+          <t>10149; 32127</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11656; 29174</t>
+          <t>10761; 29351</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>24175; 45391</t>
+          <t>28089; 53814</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>27367; 49714</t>
+          <t>26946; 50090</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>28856; 57066</t>
+          <t>29918; 55470</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>39270; 70013</t>
+          <t>40510; 71312</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>32490; 92471</t>
+          <t>60622; 89250</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>38141; 65636</t>
+          <t>38165; 66566</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>45617; 80567</t>
+          <t>44760; 78583</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>57400; 93064</t>
+          <t>56586; 93075</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>65299; 123083</t>
+          <t>94660; 132390</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>57059</t>
+          <t>57328</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>120049</t>
+          <t>126774</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>177108</t>
+          <t>184102</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>19342; 39580</t>
+          <t>19394; 38695</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>18152; 42012</t>
+          <t>18650; 42072</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>19939; 41475</t>
+          <t>20416; 41775</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>44846; 73047</t>
+          <t>45022; 74815</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>46312; 75236</t>
+          <t>44940; 76061</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>53378; 85978</t>
+          <t>53295; 85172</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>75967; 116153</t>
+          <t>74314; 115557</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>94006; 141363</t>
+          <t>110279; 143885</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>70647; 108393</t>
+          <t>71454; 107685</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>78919; 118363</t>
+          <t>78247; 118963</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>103190; 147709</t>
+          <t>101062; 148479</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>152764; 204919</t>
+          <t>164179; 206096</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>167783</t>
+          <t>181771</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>359919</t>
+          <t>387229</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>527702</t>
+          <t>569001</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>50187; 82874</t>
+          <t>51342; 83533</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>54220; 88623</t>
+          <t>51830; 89358</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>71362; 109099</t>
+          <t>72586; 113046</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>129731; 193911</t>
+          <t>158617; 210388</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>118361; 165057</t>
+          <t>118772; 165490</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>196652; 251511</t>
+          <t>196237; 252201</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>234505; 301382</t>
+          <t>237364; 302058</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>291033; 399005</t>
+          <t>357335; 418483</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>176275; 233535</t>
+          <t>180315; 234048</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>263880; 331559</t>
+          <t>260782; 331267</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>320372; 396633</t>
+          <t>320580; 395757</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>459592; 580537</t>
+          <t>529545; 610851</t>
         </is>
       </c>
     </row>
